--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6729,0.0081,0.4523,0.0074</t>
-  </si>
-  <si>
-    <t>0.4830,0.0081,0.5197,0.0251</t>
-  </si>
-  <si>
-    <t>0.5555,0.0060,0.4596,0.0211</t>
-  </si>
-  <si>
-    <t>0.8606,0.0023,0.2235,0.0035</t>
-  </si>
-  <si>
-    <t>0.8545,0.0068,0.1656,0.0135</t>
-  </si>
-  <si>
-    <t>0.9426,0.0033,0.0442,0.0105</t>
-  </si>
-  <si>
-    <t>0.8588,0.0102,0.1783,0.0106</t>
-  </si>
-  <si>
-    <t>0.9118,0.0032,0.1021,0.0064</t>
-  </si>
-  <si>
-    <t>0.8595,0.0064,0.1843,0.0094</t>
-  </si>
-  <si>
-    <t>0.9106,0.0076,0.0926,0.0085</t>
-  </si>
-  <si>
-    <t>0.8543,0.0066,0.1663,0.0178</t>
-  </si>
-  <si>
-    <t>0.9054,0.0044,0.0920,0.0093</t>
-  </si>
-  <si>
-    <t>0.4427,0.0056,0.6496,0.0065</t>
-  </si>
-  <si>
-    <t>0.3320,0.0066,0.7756,0.0058</t>
-  </si>
-  <si>
-    <t>0.3316,0.0079,0.7800,0.0045</t>
-  </si>
-  <si>
-    <t>0.5655,0.0088,0.5859,0.0054</t>
-  </si>
-  <si>
-    <t>0.5207,0.0064,0.5999,0.0063</t>
-  </si>
-  <si>
-    <t>0.5261,0.0400,0.5110,0.0085</t>
-  </si>
-  <si>
-    <t>0.6794,0.0608,0.3350,0.0056</t>
-  </si>
-  <si>
-    <t>0.6238,0.0222,0.4858,0.0072</t>
-  </si>
-  <si>
-    <t>0.6239,0.0346,0.4506,0.0046</t>
-  </si>
-  <si>
-    <t>0.7582,0.0112,0.3865,0.0030</t>
-  </si>
-  <si>
-    <t>0.4194,0.0072,0.6823,0.0051</t>
-  </si>
-  <si>
-    <t>0.4546,0.0145,0.6292,0.0086</t>
-  </si>
-  <si>
-    <t>0.1973,0.0233,0.8410,0.0044</t>
-  </si>
-  <si>
-    <t>0.4127,0.0084,0.6907,0.0074</t>
-  </si>
-  <si>
-    <t>0.3508,0.0074,0.7838,0.0029</t>
-  </si>
-  <si>
-    <t>0.1907,0.0336,0.8456,0.0053</t>
-  </si>
-  <si>
-    <t>0.0966,0.0079,0.9149,0.0088</t>
-  </si>
-  <si>
-    <t>0.6630,0.0137,0.5070,0.0038</t>
-  </si>
-  <si>
-    <t>0.6511,0.0071,0.5045,0.0052</t>
-  </si>
-  <si>
-    <t>0.0693,0.0187,0.9431,0.0045</t>
-  </si>
-  <si>
-    <t>0.4892,0.0364,0.6184,0.0044</t>
-  </si>
-  <si>
-    <t>0.7649,0.0134,0.3341,0.0071</t>
-  </si>
-  <si>
-    <t>0.4160,0.0164,0.7301,0.0143</t>
-  </si>
-  <si>
-    <t>0.7788,0.0059,0.3546,0.0039</t>
-  </si>
-  <si>
-    <t>0.6482,0.0265,0.4952,0.0061</t>
-  </si>
-  <si>
-    <t>0.0747,0.2437,0.7995,0.0095</t>
-  </si>
-  <si>
-    <t>0.1712,0.0147,0.8592,0.0100</t>
-  </si>
-  <si>
-    <t>0.0336,0.0598,0.9608,0.0033</t>
-  </si>
-  <si>
-    <t>0.0965,0.0060,0.9042,0.0100</t>
-  </si>
-  <si>
-    <t>0.2827,0.0178,0.7962,0.0059</t>
-  </si>
-  <si>
-    <t>0.0246,0.6362,0.8026,0.0030</t>
-  </si>
-  <si>
-    <t>0.1228,0.0127,0.9276,0.0037</t>
-  </si>
-  <si>
-    <t>0.6422,0.0081,0.4594,0.0113</t>
-  </si>
-  <si>
-    <t>0.4399,0.0939,0.5006,0.0047</t>
-  </si>
-  <si>
-    <t>0.4061,0.0950,0.5525,0.0057</t>
-  </si>
-  <si>
-    <t>0.4861,0.1124,0.4514,0.0090</t>
-  </si>
-  <si>
-    <t>0.0132,0.1663,0.9699,0.0014</t>
-  </si>
-  <si>
-    <t>0.0293,0.1092,0.9528,0.0015</t>
-  </si>
-  <si>
-    <t>0.1129,0.0102,0.9210,0.0043</t>
-  </si>
-  <si>
-    <t>0.2013,0.0115,0.8423,0.0061</t>
-  </si>
-  <si>
-    <t>0.0589,0.0173,0.9459,0.0061</t>
-  </si>
-  <si>
-    <t>0.1782,0.0128,0.8637,0.0071</t>
-  </si>
-  <si>
-    <t>0.8430,0.0084,0.2358,0.0047</t>
-  </si>
-  <si>
-    <t>0.8051,0.0051,0.2531,0.0093</t>
-  </si>
-  <si>
-    <t>0.9278,0.0051,0.0690,0.0075</t>
-  </si>
-  <si>
-    <t>0.2462,0.0096,0.8772,0.0086</t>
-  </si>
-  <si>
-    <t>0.8505,0.0065,0.1892,0.0099</t>
-  </si>
-  <si>
-    <t>0.9210,0.0055,0.0835,0.0072</t>
-  </si>
-  <si>
-    <t>0.8333,0.0066,0.1904,0.0151</t>
-  </si>
-  <si>
-    <t>0.0362,0.3841,0.8836,0.0026</t>
-  </si>
-  <si>
-    <t>0.0745,0.0369,0.9312,0.0050</t>
-  </si>
-  <si>
-    <t>0.0390,0.0851,0.9460,0.0034</t>
-  </si>
-  <si>
-    <t>0.0126,0.4838,0.9403,0.0013</t>
-  </si>
-  <si>
-    <t>0.0495,0.0257,0.9631,0.0029</t>
-  </si>
-  <si>
-    <t>0.6300,0.0293,0.4819,0.0072</t>
-  </si>
-  <si>
-    <t>0.0188,0.9519,0.2498,0.0011</t>
-  </si>
-  <si>
-    <t>0.7524,0.0047,0.4217,0.0039</t>
-  </si>
-  <si>
-    <t>0.7280,0.0081,0.4023,0.0051</t>
-  </si>
-  <si>
-    <t>0.2600,0.0297,0.8090,0.0062</t>
-  </si>
-  <si>
-    <t>0.0726,0.1577,0.8751,0.0045</t>
-  </si>
-  <si>
-    <t>0.0548,0.1740,0.9112,0.0042</t>
-  </si>
-  <si>
-    <t>0.0130,0.7941,0.8051,0.0021</t>
-  </si>
-  <si>
-    <t>0.0123,0.7676,0.8684,0.0012</t>
-  </si>
-  <si>
-    <t>0.4356,0.0019,0.5034,0.0216</t>
-  </si>
-  <si>
-    <t>0.5893,0.0020,0.4264,0.0138</t>
-  </si>
-  <si>
-    <t>0.5963,0.0021,0.4298,0.0125</t>
-  </si>
-  <si>
-    <t>0.4307,0.0028,0.6094,0.0120</t>
-  </si>
-  <si>
-    <t>0.7368,0.0030,0.3838,0.0056</t>
-  </si>
-  <si>
-    <t>0.7085,0.0027,0.3187,0.0134</t>
-  </si>
-  <si>
-    <t>0.0257,0.1727,0.9487,0.0017</t>
-  </si>
-  <si>
-    <t>0.0221,0.3252,0.9460,0.0018</t>
-  </si>
-  <si>
-    <t>0.0183,0.3778,0.9310,0.0011</t>
-  </si>
-  <si>
-    <t>0.0551,0.0459,0.9369,0.0054</t>
-  </si>
-  <si>
-    <t>0.0443,0.4280,0.8445,0.0031</t>
-  </si>
-  <si>
-    <t>0.0379,0.1500,0.9341,0.0026</t>
-  </si>
-  <si>
-    <t>0.8903,0.0039,0.0932,0.0150</t>
-  </si>
-  <si>
-    <t>0.9001,0.0031,0.1590,0.0033</t>
-  </si>
-  <si>
-    <t>0.8599,0.0061,0.1605,0.0109</t>
-  </si>
-  <si>
-    <t>0.8864,0.0034,0.1741,0.0051</t>
-  </si>
-  <si>
-    <t>0.8852,0.0129,0.1212,0.0140</t>
-  </si>
-  <si>
-    <t>0.9012,0.0054,0.0861,0.0110</t>
-  </si>
-  <si>
-    <t>0.8153,0.0059,0.2000,0.0157</t>
-  </si>
-  <si>
-    <t>0.8519,0.0045,0.2392,0.0041</t>
-  </si>
-  <si>
-    <t>0.8587,0.0062,0.1900,0.0099</t>
-  </si>
-  <si>
-    <t>0.8696,0.0032,0.1498,0.0102</t>
-  </si>
-  <si>
-    <t>0.9144,0.0035,0.0899,0.0071</t>
-  </si>
-  <si>
-    <t>0.8929,0.0029,0.0756,0.0182</t>
-  </si>
-  <si>
-    <t>0.9329,0.0031,0.0590,0.0090</t>
-  </si>
-  <si>
-    <t>0.8676,0.0054,0.1278,0.0209</t>
-  </si>
-  <si>
-    <t>0.9258,0.0058,0.0727,0.0086</t>
-  </si>
-  <si>
-    <t>0.8627,0.0032,0.1989,0.0070</t>
-  </si>
-  <si>
-    <t>0.1617,0.0111,0.8904,0.0077</t>
-  </si>
-  <si>
-    <t>0.3140,0.0064,0.7669,0.0066</t>
-  </si>
-  <si>
-    <t>0.5531,0.0064,0.5640,0.0066</t>
-  </si>
-  <si>
-    <t>0.2769,0.0109,0.8148,0.0043</t>
-  </si>
-  <si>
-    <t>0.7293,0.0175,0.3731,0.0060</t>
-  </si>
-  <si>
-    <t>0.4536,0.1762,0.3794,0.0093</t>
-  </si>
-  <si>
-    <t>0.8492,0.0108,0.1986,0.0055</t>
-  </si>
-  <si>
-    <t>0.8018,0.0061,0.3045,0.0049</t>
-  </si>
-  <si>
-    <t>0.7459,0.0205,0.3466,0.0052</t>
-  </si>
-  <si>
-    <t>0.4550,0.1087,0.4970,0.0071</t>
-  </si>
-  <si>
-    <t>0.7103,0.0066,0.4632,0.0034</t>
-  </si>
-  <si>
-    <t>0.5503,0.0094,0.6480,0.0041</t>
-  </si>
-  <si>
-    <t>0.2569,0.0030,0.8145,0.0051</t>
-  </si>
-  <si>
-    <t>0.4115,0.0098,0.6806,0.0056</t>
-  </si>
-  <si>
-    <t>0.4892,0.0074,0.6248,0.0062</t>
-  </si>
-  <si>
-    <t>0.5099,0.0108,0.6158,0.0095</t>
-  </si>
-  <si>
-    <t>0.4254,0.1203,0.4727,0.0047</t>
-  </si>
-  <si>
-    <t>0.2376,0.3700,0.4637,0.0054</t>
-  </si>
-  <si>
-    <t>0.3554,0.0085,0.7137,0.0095</t>
-  </si>
-  <si>
-    <t>0.0580,0.8048,0.4573,0.0024</t>
-  </si>
-  <si>
-    <t>0.6913,0.0160,0.4316,0.0052</t>
-  </si>
-  <si>
-    <t>0.8567,0.0059,0.2080,0.0045</t>
-  </si>
-  <si>
-    <t>0.7306,0.0204,0.3564,0.0070</t>
-  </si>
-  <si>
-    <t>0.8503,0.0050,0.2303,0.0056</t>
-  </si>
-  <si>
-    <t>0.8874,0.0036,0.1324,0.0087</t>
-  </si>
-  <si>
-    <t>0.8700,0.0039,0.1619,0.0076</t>
-  </si>
-  <si>
-    <t>0.9040,0.0038,0.1316,0.0052</t>
-  </si>
-  <si>
-    <t>0.8718,0.0026,0.1794,0.0057</t>
-  </si>
-  <si>
-    <t>0.7906,0.0068,0.3398,0.0043</t>
-  </si>
-  <si>
-    <t>0.7585,0.0061,0.3456,0.0108</t>
-  </si>
-  <si>
-    <t>0.6680,0.0062,0.4775,0.0086</t>
-  </si>
-  <si>
-    <t>0.0551,0.0929,0.9268,0.0038</t>
-  </si>
-  <si>
-    <t>0.0979,0.0658,0.8929,0.0028</t>
-  </si>
-  <si>
-    <t>0.0750,0.0215,0.9366,0.0050</t>
-  </si>
-  <si>
-    <t>0.0952,0.0947,0.8704,0.0045</t>
-  </si>
-  <si>
-    <t>0.6159,0.0030,0.4713,0.0081</t>
-  </si>
-  <si>
-    <t>0.5176,0.0043,0.6739,0.0034</t>
-  </si>
-  <si>
-    <t>0.5114,0.0042,0.6714,0.0042</t>
-  </si>
-  <si>
-    <t>0.4303,0.0075,0.6620,0.0084</t>
-  </si>
-  <si>
-    <t>0.6906,0.0034,0.3633,0.0098</t>
-  </si>
-  <si>
-    <t>0.3195,0.0020,0.4274,0.0827</t>
-  </si>
-  <si>
-    <t>0.3315,0.0034,0.5780,0.0385</t>
-  </si>
-  <si>
-    <t>0.5167,0.0031,0.5100,0.0161</t>
-  </si>
-  <si>
-    <t>0.0147,0.4381,0.9386,0.0016</t>
-  </si>
-  <si>
-    <t>0.9229,0.0058,0.0928,0.0046</t>
-  </si>
-  <si>
-    <t>0.7794,0.0056,0.3430,0.0041</t>
-  </si>
-  <si>
-    <t>0.8839,0.0061,0.1617,0.0051</t>
-  </si>
-  <si>
-    <t>0.8063,0.0068,0.2345,0.0118</t>
-  </si>
-  <si>
-    <t>0.8520,0.0054,0.1841,0.0092</t>
-  </si>
-  <si>
-    <t>0.7214,0.0036,0.3299,0.0100</t>
-  </si>
-  <si>
-    <t>0.7882,0.0057,0.3110,0.0057</t>
-  </si>
-  <si>
-    <t>0.1011,0.0126,0.9320,0.0055</t>
-  </si>
-  <si>
-    <t>0.5584,0.0038,0.4148,0.0227</t>
-  </si>
-  <si>
-    <t>0.8067,0.0040,0.2457,0.0085</t>
-  </si>
-  <si>
-    <t>0.7934,0.0077,0.3187,0.0039</t>
-  </si>
-  <si>
-    <t>0.7074,0.0060,0.3895,0.0068</t>
-  </si>
-  <si>
-    <t>0.7187,0.0073,0.4153,0.0061</t>
-  </si>
-  <si>
-    <t>0.6819,0.0065,0.4616,0.0041</t>
-  </si>
-  <si>
-    <t>0.8017,0.0053,0.2979,0.0032</t>
-  </si>
-  <si>
-    <t>0.7679,0.0103,0.3353,0.0053</t>
-  </si>
-  <si>
-    <t>0.8625,0.0058,0.1469,0.0147</t>
-  </si>
-  <si>
-    <t>0.8865,0.0054,0.1399,0.0120</t>
-  </si>
-  <si>
-    <t>0.8981,0.0035,0.1299,0.0068</t>
-  </si>
-  <si>
-    <t>0.7807,0.0050,0.2834,0.0129</t>
-  </si>
-  <si>
-    <t>0.8432,0.0044,0.2023,0.0085</t>
-  </si>
-  <si>
-    <t>0.8308,0.0033,0.1861,0.0131</t>
-  </si>
-  <si>
-    <t>0.7758,0.0076,0.2671,0.0175</t>
-  </si>
-  <si>
-    <t>0.8071,0.0035,0.3331,0.0040</t>
-  </si>
-  <si>
-    <t>0.8659,0.0121,0.1689,0.0058</t>
-  </si>
-  <si>
-    <t>0.8243,0.0061,0.2631,0.0055</t>
-  </si>
-  <si>
-    <t>0.8731,0.0049,0.1693,0.0048</t>
-  </si>
-  <si>
-    <t>0.6854,0.0084,0.4403,0.0075</t>
-  </si>
-  <si>
-    <t>0.8670,0.0025,0.2272,0.0033</t>
-  </si>
-  <si>
-    <t>0.8814,0.0037,0.1643,0.0034</t>
-  </si>
-  <si>
-    <t>0.8691,0.0062,0.1978,0.0059</t>
-  </si>
-  <si>
-    <t>0.8326,0.0046,0.2663,0.0050</t>
-  </si>
-  <si>
-    <t>0.0759,0.0223,0.9392,0.0066</t>
-  </si>
-  <si>
-    <t>0.7619,0.0090,0.3292,0.0097</t>
-  </si>
-  <si>
-    <t>0.1162,0.0399,0.8938,0.0043</t>
-  </si>
-  <si>
-    <t>0.0436,0.0403,0.9568,0.0040</t>
-  </si>
-  <si>
-    <t>0.4489,0.0089,0.6703,0.0070</t>
-  </si>
-  <si>
-    <t>0.0738,0.0922,0.8987,0.0035</t>
-  </si>
-  <si>
-    <t>0.1818,0.0299,0.8552,0.0052</t>
-  </si>
-  <si>
-    <t>0.1532,0.0089,0.8858,0.0052</t>
-  </si>
-  <si>
-    <t>0.3132,0.0112,0.7599,0.0058</t>
-  </si>
-  <si>
-    <t>0.6968,0.0100,0.4372,0.0061</t>
-  </si>
-  <si>
-    <t>0.4758,0.0126,0.6608,0.0060</t>
-  </si>
-  <si>
-    <t>0.7557,0.0039,0.4061,0.0026</t>
-  </si>
-  <si>
-    <t>0.5062,0.0172,0.6183,0.0062</t>
-  </si>
-  <si>
-    <t>0.5069,0.0198,0.6022,0.0074</t>
-  </si>
-  <si>
-    <t>0.5399,0.0077,0.5856,0.0071</t>
-  </si>
-  <si>
-    <t>0.5807,0.0102,0.5637,0.0047</t>
-  </si>
-  <si>
-    <t>0.6745,0.0078,0.4553,0.0046</t>
-  </si>
-  <si>
-    <t>0.8222,0.0094,0.2858,0.0079</t>
-  </si>
-  <si>
-    <t>0.8686,0.0067,0.2066,0.0041</t>
-  </si>
-  <si>
-    <t>0.8484,0.0142,0.1892,0.0079</t>
-  </si>
-  <si>
-    <t>0.8641,0.0089,0.1724,0.0091</t>
-  </si>
-  <si>
-    <t>0.9025,0.0076,0.1135,0.0073</t>
-  </si>
-  <si>
-    <t>0.5107,0.0079,0.6478,0.0040</t>
-  </si>
-  <si>
-    <t>0.5206,0.0034,0.6031,0.0051</t>
-  </si>
-  <si>
-    <t>0.6520,0.0037,0.5280,0.0025</t>
-  </si>
-  <si>
-    <t>0.5133,0.0071,0.6233,0.0051</t>
-  </si>
-  <si>
-    <t>0.6038,0.0054,0.5386,0.0047</t>
-  </si>
-  <si>
-    <t>0.2813,0.0101,0.8010,0.0053</t>
-  </si>
-  <si>
-    <t>0.3269,0.0369,0.7061,0.0120</t>
-  </si>
-  <si>
-    <t>0.1162,0.0490,0.8972,0.0039</t>
-  </si>
-  <si>
-    <t>0.1808,0.0057,0.8572,0.0096</t>
-  </si>
-  <si>
-    <t>0.1139,0.0603,0.8647,0.0060</t>
-  </si>
-  <si>
-    <t>0.8398,0.0098,0.2003,0.0134</t>
-  </si>
-  <si>
-    <t>0.8410,0.0041,0.1585,0.0134</t>
-  </si>
-  <si>
-    <t>0.8596,0.0070,0.1920,0.0098</t>
-  </si>
-  <si>
-    <t>0.8641,0.0069,0.1848,0.0078</t>
-  </si>
-  <si>
-    <t>0.8572,0.0044,0.1933,0.0067</t>
-  </si>
-  <si>
-    <t>0.9181,0.0051,0.0938,0.0059</t>
-  </si>
-  <si>
-    <t>0.9137,0.0050,0.0694,0.0101</t>
-  </si>
-  <si>
-    <t>0.9032,0.0078,0.0880,0.0131</t>
-  </si>
-  <si>
-    <t>0.1934,0.0163,0.8557,0.0069</t>
-  </si>
-  <si>
-    <t>0.6198,0.0108,0.4531,0.0136</t>
-  </si>
-  <si>
-    <t>0.8095,0.0057,0.2935,0.0056</t>
-  </si>
-  <si>
-    <t>0.0894,0.0171,0.9283,0.0054</t>
-  </si>
-  <si>
-    <t>0.0129,0.0312,0.9847,0.0027</t>
-  </si>
-  <si>
-    <t>0.2648,0.0203,0.7941,0.0089</t>
-  </si>
-  <si>
-    <t>0.0207,0.0214,0.9812,0.0024</t>
-  </si>
-  <si>
-    <t>0.3024,0.0083,0.7974,0.0039</t>
-  </si>
-  <si>
-    <t>0.0382,0.0653,0.9574,0.0047</t>
-  </si>
-  <si>
-    <t>0.0484,0.0294,0.9517,0.0032</t>
-  </si>
-  <si>
-    <t>0.0851,0.0184,0.9495,0.0029</t>
-  </si>
-  <si>
-    <t>0.5595,0.0031,0.6343,0.0028</t>
-  </si>
-  <si>
-    <t>0.4086,0.0037,0.7255,0.0041</t>
-  </si>
-  <si>
-    <t>0.5400,0.0025,0.5715,0.0060</t>
-  </si>
-  <si>
-    <t>0.9242,0.0033,0.0965,0.0050</t>
-  </si>
-  <si>
-    <t>0.7981,0.0077,0.2963,0.0091</t>
-  </si>
-  <si>
-    <t>0.8482,0.0071,0.2195,0.0082</t>
-  </si>
-  <si>
-    <t>0.9017,0.0043,0.1348,0.0051</t>
-  </si>
-  <si>
-    <t>0.8700,0.0041,0.1211,0.0130</t>
-  </si>
-  <si>
-    <t>0.8342,0.0098,0.2410,0.0060</t>
-  </si>
-  <si>
-    <t>0.9048,0.0055,0.1252,0.0069</t>
-  </si>
-  <si>
-    <t>0.9079,0.0051,0.1058,0.0057</t>
-  </si>
-  <si>
-    <t>0.2240,0.0452,0.7957,0.0057</t>
-  </si>
-  <si>
-    <t>0.0285,0.0708,0.9550,0.0048</t>
-  </si>
-  <si>
-    <t>0.1572,0.0408,0.8648,0.0044</t>
-  </si>
-  <si>
-    <t>0.3450,0.0346,0.6983,0.0074</t>
-  </si>
-  <si>
-    <t>0.1358,0.0094,0.9029,0.0055</t>
-  </si>
-  <si>
-    <t>0.2705,0.0093,0.7353,0.0218</t>
-  </si>
-  <si>
-    <t>0.4106,0.0097,0.6890,0.0072</t>
-  </si>
-  <si>
-    <t>0.0562,0.0277,0.9302,0.0114</t>
-  </si>
-  <si>
-    <t>0.7130,0.0029,0.3212,0.0103</t>
-  </si>
-  <si>
-    <t>0.5101,0.0036,0.4870,0.0173</t>
-  </si>
-  <si>
-    <t>0.6761,0.0023,0.4171,0.0073</t>
-  </si>
-  <si>
-    <t>0.5216,0.0031,0.3491,0.0427</t>
-  </si>
-  <si>
-    <t>0.5486,0.0026,0.3918,0.0294</t>
-  </si>
-  <si>
-    <t>0.5409,0.0036,0.5163,0.0079</t>
+    <t>0.7910,0.0582,0.1437,0.0640</t>
+  </si>
+  <si>
+    <t>0.0137,0.0078,0.0068,0.9881</t>
+  </si>
+  <si>
+    <t>0.3496,0.0257,0.0537,0.6239</t>
+  </si>
+  <si>
+    <t>0.1716,0.0147,0.0412,0.8087</t>
+  </si>
+  <si>
+    <t>0.9883,0.0078,0.0023,0.0031</t>
+  </si>
+  <si>
+    <t>0.9922,0.0035,0.0009,0.0028</t>
+  </si>
+  <si>
+    <t>0.9804,0.0161,0.0041,0.0040</t>
+  </si>
+  <si>
+    <t>0.9882,0.0066,0.0017,0.0034</t>
+  </si>
+  <si>
+    <t>0.9842,0.0127,0.0037,0.0027</t>
+  </si>
+  <si>
+    <t>0.9874,0.0088,0.0020,0.0031</t>
+  </si>
+  <si>
+    <t>0.9925,0.0058,0.0009,0.0018</t>
+  </si>
+  <si>
+    <t>0.9875,0.0072,0.0029,0.0031</t>
+  </si>
+  <si>
+    <t>0.6526,0.0245,0.4755,0.0049</t>
+  </si>
+  <si>
+    <t>0.0467,0.0261,0.9260,0.0187</t>
+  </si>
+  <si>
+    <t>0.1340,0.0126,0.9014,0.0081</t>
+  </si>
+  <si>
+    <t>0.0224,0.0368,0.9625,0.0038</t>
+  </si>
+  <si>
+    <t>0.6108,0.0355,0.4726,0.0116</t>
+  </si>
+  <si>
+    <t>0.0051,0.9929,0.0099,0.0004</t>
+  </si>
+  <si>
+    <t>0.0099,0.9876,0.0161,0.0005</t>
+  </si>
+  <si>
+    <t>0.3980,0.5469,0.0616,0.0039</t>
+  </si>
+  <si>
+    <t>0.0145,0.9853,0.0081,0.0007</t>
+  </si>
+  <si>
+    <t>0.0035,0.9952,0.0063,0.0003</t>
+  </si>
+  <si>
+    <t>0.2549,0.0348,0.7373,0.0313</t>
+  </si>
+  <si>
+    <t>0.1838,0.1498,0.6541,0.0407</t>
+  </si>
+  <si>
+    <t>0.0117,0.0052,0.9840,0.0094</t>
+  </si>
+  <si>
+    <t>0.0780,0.0340,0.8942,0.0210</t>
+  </si>
+  <si>
+    <t>0.1057,0.0093,0.9197,0.0074</t>
+  </si>
+  <si>
+    <t>0.0895,0.0086,0.9254,0.0125</t>
+  </si>
+  <si>
+    <t>0.0096,0.0050,0.9845,0.0144</t>
+  </si>
+  <si>
+    <t>0.1561,0.6771,0.1405,0.0054</t>
+  </si>
+  <si>
+    <t>0.1759,0.1044,0.7303,0.0095</t>
+  </si>
+  <si>
+    <t>0.0007,0.0319,0.9977,0.0015</t>
+  </si>
+  <si>
+    <t>0.0032,0.9346,0.5243,0.0008</t>
+  </si>
+  <si>
+    <t>0.7073,0.0333,0.2903,0.0289</t>
+  </si>
+  <si>
+    <t>0.1651,0.0579,0.8128,0.0567</t>
+  </si>
+  <si>
+    <t>0.7003,0.3391,0.0272,0.0061</t>
+  </si>
+  <si>
+    <t>0.0271,0.8519,0.5560,0.0041</t>
+  </si>
+  <si>
+    <t>0.0256,0.8861,0.2399,0.0135</t>
+  </si>
+  <si>
+    <t>0.0262,0.1324,0.8947,0.0437</t>
+  </si>
+  <si>
+    <t>0.0300,0.0302,0.9341,0.0348</t>
+  </si>
+  <si>
+    <t>0.0249,0.1072,0.9196,0.0294</t>
+  </si>
+  <si>
+    <t>0.0283,0.1833,0.9406,0.0077</t>
+  </si>
+  <si>
+    <t>0.0020,0.9864,0.2166,0.0007</t>
+  </si>
+  <si>
+    <t>0.0472,0.0841,0.9337,0.0086</t>
+  </si>
+  <si>
+    <t>0.0405,0.3650,0.0219,0.8615</t>
+  </si>
+  <si>
+    <t>0.0008,0.9961,0.0141,0.0023</t>
+  </si>
+  <si>
+    <t>0.0015,0.9934,0.0343,0.0028</t>
+  </si>
+  <si>
+    <t>0.0009,0.9968,0.0271,0.0007</t>
+  </si>
+  <si>
+    <t>0.0067,0.4421,0.9596,0.0039</t>
+  </si>
+  <si>
+    <t>0.0032,0.0956,0.9894,0.0040</t>
+  </si>
+  <si>
+    <t>0.0455,0.0338,0.9260,0.0290</t>
+  </si>
+  <si>
+    <t>0.0767,0.0026,0.9423,0.0083</t>
+  </si>
+  <si>
+    <t>0.0342,0.0903,0.9128,0.0347</t>
+  </si>
+  <si>
+    <t>0.0115,0.3124,0.9429,0.0059</t>
+  </si>
+  <si>
+    <t>0.9583,0.0363,0.0117,0.0060</t>
+  </si>
+  <si>
+    <t>0.9852,0.0109,0.0034,0.0032</t>
+  </si>
+  <si>
+    <t>0.8973,0.0362,0.0687,0.0056</t>
+  </si>
+  <si>
+    <t>0.0089,0.0772,0.9835,0.0097</t>
+  </si>
+  <si>
+    <t>0.9811,0.0101,0.0065,0.0037</t>
+  </si>
+  <si>
+    <t>0.9876,0.0060,0.0028,0.0042</t>
+  </si>
+  <si>
+    <t>0.9238,0.0967,0.0081,0.0031</t>
+  </si>
+  <si>
+    <t>0.0031,0.9692,0.5555,0.0012</t>
+  </si>
+  <si>
+    <t>0.0077,0.1848,0.9744,0.0073</t>
+  </si>
+  <si>
+    <t>0.0093,0.0267,0.9789,0.0137</t>
+  </si>
+  <si>
+    <t>0.0041,0.8022,0.9369,0.0016</t>
+  </si>
+  <si>
+    <t>0.0045,0.0112,0.9924,0.0049</t>
+  </si>
+  <si>
+    <t>0.0379,0.8462,0.3878,0.0056</t>
+  </si>
+  <si>
+    <t>0.0009,0.9976,0.0055,0.0001</t>
+  </si>
+  <si>
+    <t>0.6270,0.0187,0.4718,0.0150</t>
+  </si>
+  <si>
+    <t>0.2291,0.0443,0.7900,0.0117</t>
+  </si>
+  <si>
+    <t>0.0137,0.0341,0.9802,0.0050</t>
+  </si>
+  <si>
+    <t>0.0016,0.9790,0.6476,0.0007</t>
+  </si>
+  <si>
+    <t>0.0091,0.7290,0.8783,0.0024</t>
+  </si>
+  <si>
+    <t>0.0021,0.9845,0.3744,0.0010</t>
+  </si>
+  <si>
+    <t>0.0016,0.9106,0.9333,0.0006</t>
+  </si>
+  <si>
+    <t>0.0447,0.0081,0.0599,0.9367</t>
+  </si>
+  <si>
+    <t>0.0086,0.0128,0.0146,0.9888</t>
+  </si>
+  <si>
+    <t>0.0075,0.0085,0.0105,0.9915</t>
+  </si>
+  <si>
+    <t>0.0170,0.0324,0.0233,0.9767</t>
+  </si>
+  <si>
+    <t>0.0142,0.0076,0.0183,0.9847</t>
+  </si>
+  <si>
+    <t>0.0092,0.0084,0.0299,0.9843</t>
+  </si>
+  <si>
+    <t>0.0019,0.9379,0.8835,0.0005</t>
+  </si>
+  <si>
+    <t>0.0032,0.7800,0.9427,0.0008</t>
+  </si>
+  <si>
+    <t>0.0162,0.8895,0.4684,0.0132</t>
+  </si>
+  <si>
+    <t>0.0065,0.6511,0.9286,0.0020</t>
+  </si>
+  <si>
+    <t>0.0035,0.9395,0.7038,0.0008</t>
+  </si>
+  <si>
+    <t>0.0076,0.8135,0.8518,0.0022</t>
+  </si>
+  <si>
+    <t>0.9863,0.0123,0.0026,0.0028</t>
+  </si>
+  <si>
+    <t>0.9856,0.0103,0.0034,0.0029</t>
+  </si>
+  <si>
+    <t>0.9883,0.0094,0.0020,0.0016</t>
+  </si>
+  <si>
+    <t>0.9917,0.0038,0.0015,0.0026</t>
+  </si>
+  <si>
+    <t>0.9839,0.0104,0.0040,0.0028</t>
+  </si>
+  <si>
+    <t>0.9902,0.0064,0.0014,0.0026</t>
+  </si>
+  <si>
+    <t>0.9825,0.0142,0.0047,0.0035</t>
+  </si>
+  <si>
+    <t>0.9887,0.0085,0.0018,0.0022</t>
+  </si>
+  <si>
+    <t>0.9921,0.0041,0.0012,0.0023</t>
+  </si>
+  <si>
+    <t>0.9890,0.0070,0.0028,0.0019</t>
+  </si>
+  <si>
+    <t>0.9924,0.0037,0.0008,0.0027</t>
+  </si>
+  <si>
+    <t>0.9918,0.0041,0.0014,0.0026</t>
+  </si>
+  <si>
+    <t>0.9914,0.0042,0.0013,0.0029</t>
+  </si>
+  <si>
+    <t>0.9909,0.0046,0.0020,0.0027</t>
+  </si>
+  <si>
+    <t>0.9842,0.0093,0.0034,0.0038</t>
+  </si>
+  <si>
+    <t>0.9920,0.0040,0.0011,0.0027</t>
+  </si>
+  <si>
+    <t>0.0020,0.0051,0.9961,0.0057</t>
+  </si>
+  <si>
+    <t>0.1012,0.0153,0.9154,0.0058</t>
+  </si>
+  <si>
+    <t>0.5889,0.0288,0.3908,0.0442</t>
+  </si>
+  <si>
+    <t>0.0464,0.0055,0.9557,0.0071</t>
+  </si>
+  <si>
+    <t>0.0098,0.9826,0.0214,0.0007</t>
+  </si>
+  <si>
+    <t>0.0193,0.9728,0.0366,0.0009</t>
+  </si>
+  <si>
+    <t>0.0474,0.9617,0.0077,0.0013</t>
+  </si>
+  <si>
+    <t>0.1180,0.8983,0.0143,0.0029</t>
+  </si>
+  <si>
+    <t>0.0279,0.9670,0.0155,0.0018</t>
+  </si>
+  <si>
+    <t>0.0024,0.9959,0.0050,0.0002</t>
+  </si>
+  <si>
+    <t>0.3975,0.6451,0.0200,0.0026</t>
+  </si>
+  <si>
+    <t>0.4922,0.0448,0.5464,0.0257</t>
+  </si>
+  <si>
+    <t>0.1449,0.0080,0.8997,0.0095</t>
+  </si>
+  <si>
+    <t>0.4368,0.0710,0.5591,0.0353</t>
+  </si>
+  <si>
+    <t>0.3320,0.1762,0.5018,0.0208</t>
+  </si>
+  <si>
+    <t>0.1736,0.0902,0.0746,0.7824</t>
+  </si>
+  <si>
+    <t>0.0015,0.9966,0.0070,0.0006</t>
+  </si>
+  <si>
+    <t>0.0007,0.9969,0.0088,0.0015</t>
+  </si>
+  <si>
+    <t>0.0125,0.9606,0.0624,0.0160</t>
+  </si>
+  <si>
+    <t>0.0006,0.9972,0.1202,0.0002</t>
+  </si>
+  <si>
+    <t>0.0750,0.8386,0.1654,0.0024</t>
+  </si>
+  <si>
+    <t>0.8166,0.2144,0.0203,0.0060</t>
+  </si>
+  <si>
+    <t>0.2727,0.8101,0.0199,0.0029</t>
+  </si>
+  <si>
+    <t>0.9686,0.0184,0.0077,0.0068</t>
+  </si>
+  <si>
+    <t>0.9857,0.0079,0.0034,0.0033</t>
+  </si>
+  <si>
+    <t>0.9791,0.0109,0.0075,0.0051</t>
+  </si>
+  <si>
+    <t>0.9779,0.0114,0.0057,0.0054</t>
+  </si>
+  <si>
+    <t>0.9857,0.0058,0.0038,0.0037</t>
+  </si>
+  <si>
+    <t>0.9595,0.0176,0.0204,0.0074</t>
+  </si>
+  <si>
+    <t>0.9775,0.0150,0.0030,0.0071</t>
+  </si>
+  <si>
+    <t>0.9800,0.0074,0.0056,0.0074</t>
+  </si>
+  <si>
+    <t>0.0041,0.8523,0.8922,0.0019</t>
+  </si>
+  <si>
+    <t>0.0037,0.7893,0.9361,0.0008</t>
+  </si>
+  <si>
+    <t>0.0092,0.3608,0.9400,0.0050</t>
+  </si>
+  <si>
+    <t>0.0285,0.3168,0.9015,0.0051</t>
+  </si>
+  <si>
+    <t>0.2620,0.1696,0.5251,0.0459</t>
+  </si>
+  <si>
+    <t>0.4311,0.0378,0.6178,0.0252</t>
+  </si>
+  <si>
+    <t>0.1031,0.0042,0.9286,0.0110</t>
+  </si>
+  <si>
+    <t>0.5023,0.0296,0.5841,0.0134</t>
+  </si>
+  <si>
+    <t>0.1016,0.0097,0.2757,0.6969</t>
+  </si>
+  <si>
+    <t>0.0009,0.0056,0.0169,0.9959</t>
+  </si>
+  <si>
+    <t>0.0191,0.0281,0.0346,0.9690</t>
+  </si>
+  <si>
+    <t>0.0180,0.0039,0.0126,0.9844</t>
+  </si>
+  <si>
+    <t>0.0016,0.9771,0.6695,0.0007</t>
+  </si>
+  <si>
+    <t>0.9866,0.0061,0.0024,0.0039</t>
+  </si>
+  <si>
+    <t>0.3277,0.7183,0.0261,0.0178</t>
+  </si>
+  <si>
+    <t>0.9619,0.0244,0.0115,0.0087</t>
+  </si>
+  <si>
+    <t>0.7098,0.2939,0.0404,0.0109</t>
+  </si>
+  <si>
+    <t>0.8941,0.0783,0.0324,0.0104</t>
+  </si>
+  <si>
+    <t>0.6394,0.0078,0.1811,0.0944</t>
+  </si>
+  <si>
+    <t>0.9234,0.0307,0.0512,0.0107</t>
+  </si>
+  <si>
+    <t>0.0130,0.0575,0.9743,0.0067</t>
+  </si>
+  <si>
+    <t>0.5836,0.0137,0.0260,0.4092</t>
+  </si>
+  <si>
+    <t>0.8850,0.0251,0.0518,0.0426</t>
+  </si>
+  <si>
+    <t>0.4462,0.4673,0.0905,0.0594</t>
+  </si>
+  <si>
+    <t>0.9099,0.0595,0.0320,0.0144</t>
+  </si>
+  <si>
+    <t>0.7781,0.1491,0.0682,0.0146</t>
+  </si>
+  <si>
+    <t>0.5078,0.3105,0.1667,0.0207</t>
+  </si>
+  <si>
+    <t>0.4117,0.2048,0.3170,0.0125</t>
+  </si>
+  <si>
+    <t>0.8597,0.0340,0.1273,0.0064</t>
+  </si>
+  <si>
+    <t>0.9892,0.0049,0.0025,0.0031</t>
+  </si>
+  <si>
+    <t>0.9881,0.0060,0.0021,0.0043</t>
+  </si>
+  <si>
+    <t>0.9894,0.0075,0.0015,0.0024</t>
+  </si>
+  <si>
+    <t>0.9833,0.0083,0.0043,0.0045</t>
+  </si>
+  <si>
+    <t>0.9699,0.0151,0.0065,0.0117</t>
+  </si>
+  <si>
+    <t>0.9742,0.0129,0.0085,0.0064</t>
+  </si>
+  <si>
+    <t>0.9847,0.0061,0.0037,0.0057</t>
+  </si>
+  <si>
+    <t>0.9869,0.0067,0.0024,0.0041</t>
+  </si>
+  <si>
+    <t>0.6704,0.2994,0.0565,0.0119</t>
+  </si>
+  <si>
+    <t>0.8743,0.1351,0.0176,0.0049</t>
+  </si>
+  <si>
+    <t>0.3611,0.6685,0.0317,0.0057</t>
+  </si>
+  <si>
+    <t>0.6039,0.1819,0.2233,0.0221</t>
+  </si>
+  <si>
+    <t>0.9758,0.0228,0.0046,0.0033</t>
+  </si>
+  <si>
+    <t>0.7444,0.2165,0.0595,0.0201</t>
+  </si>
+  <si>
+    <t>0.9722,0.0206,0.0067,0.0041</t>
+  </si>
+  <si>
+    <t>0.9629,0.0415,0.0056,0.0046</t>
+  </si>
+  <si>
+    <t>0.0014,0.0565,0.9960,0.0012</t>
+  </si>
+  <si>
+    <t>0.9727,0.0300,0.0038,0.0026</t>
+  </si>
+  <si>
+    <t>0.0071,0.0552,0.9841,0.0037</t>
+  </si>
+  <si>
+    <t>0.0099,0.0761,0.9796,0.0076</t>
+  </si>
+  <si>
+    <t>0.1647,0.0032,0.9104,0.0065</t>
+  </si>
+  <si>
+    <t>0.0142,0.5659,0.8826,0.0035</t>
+  </si>
+  <si>
+    <t>0.0022,0.0102,0.9949,0.0033</t>
+  </si>
+  <si>
+    <t>0.0013,0.0053,0.9973,0.0023</t>
+  </si>
+  <si>
+    <t>0.0079,0.0253,0.9821,0.0141</t>
+  </si>
+  <si>
+    <t>0.1637,0.0558,0.7452,0.0644</t>
+  </si>
+  <si>
+    <t>0.0384,0.0541,0.9423,0.0082</t>
+  </si>
+  <si>
+    <t>0.4591,0.0623,0.5408,0.0167</t>
+  </si>
+  <si>
+    <t>0.2024,0.3789,0.3835,0.0093</t>
+  </si>
+  <si>
+    <t>0.0687,0.7943,0.3224,0.0152</t>
+  </si>
+  <si>
+    <t>0.3164,0.1172,0.6067,0.0494</t>
+  </si>
+  <si>
+    <t>0.4711,0.0276,0.6199,0.0155</t>
+  </si>
+  <si>
+    <t>0.4413,0.0876,0.4591,0.0090</t>
+  </si>
+  <si>
+    <t>0.1745,0.8219,0.0498,0.0037</t>
+  </si>
+  <si>
+    <t>0.9071,0.1565,0.0055,0.0023</t>
+  </si>
+  <si>
+    <t>0.7774,0.2723,0.0200,0.0075</t>
+  </si>
+  <si>
+    <t>0.9365,0.0850,0.0073,0.0040</t>
+  </si>
+  <si>
+    <t>0.8207,0.2562,0.0116,0.0049</t>
+  </si>
+  <si>
+    <t>0.2401,0.1342,0.6101,0.0092</t>
+  </si>
+  <si>
+    <t>0.4040,0.0102,0.7314,0.0063</t>
+  </si>
+  <si>
+    <t>0.4379,0.0080,0.6301,0.0153</t>
+  </si>
+  <si>
+    <t>0.4329,0.0508,0.5865,0.0200</t>
+  </si>
+  <si>
+    <t>0.4658,0.0268,0.3121,0.1615</t>
+  </si>
+  <si>
+    <t>0.1710,0.0105,0.8089,0.0432</t>
+  </si>
+  <si>
+    <t>0.0615,0.0401,0.8423,0.0938</t>
+  </si>
+  <si>
+    <t>0.0435,0.1186,0.9161,0.0145</t>
+  </si>
+  <si>
+    <t>0.0690,0.1351,0.8546,0.0318</t>
+  </si>
+  <si>
+    <t>0.0545,0.0350,0.9036,0.0374</t>
+  </si>
+  <si>
+    <t>0.9889,0.0046,0.0011,0.0042</t>
+  </si>
+  <si>
+    <t>0.9831,0.0149,0.0030,0.0029</t>
+  </si>
+  <si>
+    <t>0.9842,0.0129,0.0032,0.0031</t>
+  </si>
+  <si>
+    <t>0.9807,0.0166,0.0039,0.0040</t>
+  </si>
+  <si>
+    <t>0.9795,0.0185,0.0045,0.0032</t>
+  </si>
+  <si>
+    <t>0.9755,0.0271,0.0055,0.0034</t>
+  </si>
+  <si>
+    <t>0.9696,0.0233,0.0102,0.0047</t>
+  </si>
+  <si>
+    <t>0.9799,0.0128,0.0044,0.0045</t>
+  </si>
+  <si>
+    <t>0.0082,0.1025,0.9736,0.0065</t>
+  </si>
+  <si>
+    <t>0.1016,0.6857,0.2721,0.0100</t>
+  </si>
+  <si>
+    <t>0.7311,0.0506,0.2495,0.0196</t>
+  </si>
+  <si>
+    <t>0.0096,0.0073,0.9880,0.0056</t>
+  </si>
+  <si>
+    <t>0.0033,0.0218,0.9894,0.0057</t>
+  </si>
+  <si>
+    <t>0.0205,0.0397,0.9580,0.0070</t>
+  </si>
+  <si>
+    <t>0.0040,0.0204,0.9926,0.0035</t>
+  </si>
+  <si>
+    <t>0.0565,0.0121,0.9405,0.0077</t>
+  </si>
+  <si>
+    <t>0.0034,0.0120,0.9910,0.0100</t>
+  </si>
+  <si>
+    <t>0.0105,0.0100,0.9832,0.0119</t>
+  </si>
+  <si>
+    <t>0.0835,0.0844,0.8599,0.0069</t>
+  </si>
+  <si>
+    <t>0.2729,0.0113,0.7453,0.0286</t>
+  </si>
+  <si>
+    <t>0.0950,0.0122,0.8909,0.0260</t>
+  </si>
+  <si>
+    <t>0.6333,0.0110,0.4729,0.0131</t>
+  </si>
+  <si>
+    <t>0.9891,0.0053,0.0024,0.0030</t>
+  </si>
+  <si>
+    <t>0.9868,0.0089,0.0027,0.0033</t>
+  </si>
+  <si>
+    <t>0.9868,0.0124,0.0019,0.0022</t>
+  </si>
+  <si>
+    <t>0.9757,0.0206,0.0064,0.0024</t>
+  </si>
+  <si>
+    <t>0.9873,0.0049,0.0026,0.0037</t>
+  </si>
+  <si>
+    <t>0.9874,0.0127,0.0021,0.0016</t>
+  </si>
+  <si>
+    <t>0.9843,0.0113,0.0037,0.0026</t>
+  </si>
+  <si>
+    <t>0.9894,0.0059,0.0020,0.0024</t>
+  </si>
+  <si>
+    <t>0.0525,0.3836,0.7350,0.0084</t>
+  </si>
+  <si>
+    <t>0.0077,0.1571,0.9690,0.0090</t>
+  </si>
+  <si>
+    <t>0.0761,0.0716,0.8926,0.0109</t>
+  </si>
+  <si>
+    <t>0.0700,0.4073,0.6559,0.0240</t>
+  </si>
+  <si>
+    <t>0.0182,0.0100,0.9694,0.0173</t>
+  </si>
+  <si>
+    <t>0.1200,0.0113,0.8011,0.0659</t>
+  </si>
+  <si>
+    <t>0.1667,0.0256,0.8562,0.0126</t>
+  </si>
+  <si>
+    <t>0.0344,0.0168,0.9010,0.0788</t>
+  </si>
+  <si>
+    <t>0.4534,0.0401,0.0559,0.4668</t>
+  </si>
+  <si>
+    <t>0.0298,0.0493,0.0106,0.9697</t>
+  </si>
+  <si>
+    <t>0.0785,0.0114,0.0336,0.9308</t>
+  </si>
+  <si>
+    <t>0.0027,0.0012,0.0100,0.9958</t>
+  </si>
+  <si>
+    <t>0.0048,0.0027,0.0086,0.9936</t>
+  </si>
+  <si>
+    <t>0.4404,0.0418,0.1562,0.3116</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1981,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
         <v>266</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2121,7 +2121,7 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
         <v>276</v>
@@ -2177,7 +2177,7 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
         <v>280</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3423,7 +3423,7 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D107" t="s">
         <v>369</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3521,7 +3521,7 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
         <v>376</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3885,7 +3885,7 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D140" t="s">
         <v>402</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
         <v>437</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4823,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
         <v>469</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5201,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D234" t="s">
         <v>496</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
@@ -5509,7 +5509,7 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
         <v>518</v>
